--- a/main_test.xlsx
+++ b/main_test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HydrogenRb\HydrogenRb\Work\tech\Agent\8_14\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EFE3D5E-346B-4B90-8671-263B0E1804CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EDDF2EB-619A-4147-8E22-C3273EBAE1F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="集成_RISCV_TOP" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="RISCV_TOP" sheetId="2" r:id="rId3"/>
     <sheet name="RISCV_CORE_TEST" sheetId="3" r:id="rId4"/>
     <sheet name="MEM_PHY" sheetId="4" r:id="rId5"/>
+    <sheet name="Gen_phy" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="88">
   <si>
     <t>分类</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -303,6 +304,227 @@
   </si>
   <si>
     <t>LANE_NUM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>new_test</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>parameter_test</t>
+  </si>
+  <si>
+    <t>parameter_test</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>paramter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GEN_PHY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>parameter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gen_var_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>input</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dat_in</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sig_out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA[i]-&gt;local_gen_var_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>模块名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>例化名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>例化次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GEN_PHY_U</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gen_var_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA[i]-&gt;local_gen_var_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <color rgb="FF098658"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <color rgb="FF098658"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <color rgb="FF098658"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <color rgb="FF098658"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <color rgb="FF098658"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <color rgb="FF098658"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <color rgb="FF098658"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <color rgb="FF098658"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>}</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -310,7 +532,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -324,6 +546,18 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="5"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="5"/>
+      <color rgb="FF098658"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -346,10 +580,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -631,7 +868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y22"/>
+  <dimension ref="A1:AH22"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="9.33203125" customWidth="1"/>
@@ -639,7 +876,7 @@
     <col min="10" max="10" width="10.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
         <v>28</v>
       </c>
@@ -672,8 +909,20 @@
         <v>28</v>
       </c>
       <c r="Y1" s="1"/>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.4">
+      <c r="AB1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -737,8 +986,26 @@
       <c r="Y2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.4">
+      <c r="AA2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -802,8 +1069,20 @@
       <c r="Y3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.4">
+      <c r="AA3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC3">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
         <v>38</v>
@@ -857,8 +1136,18 @@
       <c r="Y4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.4">
+      <c r="AA4" s="1"/>
+      <c r="AB4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.4">
       <c r="I5" s="1"/>
       <c r="J5" t="s">
         <v>16</v>
@@ -894,7 +1183,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -944,8 +1233,20 @@
       <c r="Y6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.4">
+      <c r="AA6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
       <c r="B7" t="s">
         <v>8</v>
@@ -993,8 +1294,18 @@
       <c r="Y7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.4">
+      <c r="AA7" s="1"/>
+      <c r="AB7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A8" s="1"/>
       <c r="B8" t="s">
         <v>9</v>
@@ -1049,7 +1360,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A9" s="1"/>
       <c r="B9" t="s">
         <v>10</v>
@@ -1085,7 +1396,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A10" s="1"/>
       <c r="B10" t="s">
         <v>11</v>
@@ -1093,8 +1404,14 @@
       <c r="C10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.4">
+      <c r="J10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1117,7 +1434,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>47</v>
       </c>
@@ -1140,7 +1457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A15" s="1"/>
       <c r="B15" t="s">
         <v>45</v>
@@ -1161,7 +1478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A16" s="1"/>
       <c r="B16" t="s">
         <v>46</v>
@@ -1247,12 +1564,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="O3:O8"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="S3:S8"/>
+  <mergeCells count="18">
+    <mergeCell ref="AA3:AA4"/>
+    <mergeCell ref="AA6:AA7"/>
     <mergeCell ref="X1:Y1"/>
     <mergeCell ref="W3:W8"/>
     <mergeCell ref="A3:A4"/>
@@ -1264,6 +1578,11 @@
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="O3:O8"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="S3:S8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2638,7 +2957,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F2DC5A-AAE7-49CB-BE38-CB832B2EDA63}">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.4">
@@ -3008,6 +3327,23 @@
       </c>
       <c r="F31" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>69</v>
+      </c>
+      <c r="B33" t="s">
+        <v>71</v>
+      </c>
+      <c r="D33" t="s">
+        <v>72</v>
+      </c>
+      <c r="E33">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -3021,4 +3357,159 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F86AB8F-2F52-4554-8085-AB4C7DCD1608}">
+  <dimension ref="A1:I29"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3">
+        <v>32</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A4" s="1"/>
+      <c r="B4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4">
+        <v>32</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A7" s="1"/>
+      <c r="B7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="1"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A16" s="1"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A17" s="1"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A18" s="1"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A20" s="1"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A21" s="1"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A22" s="1"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A23" s="1"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A24" s="1"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A25" s="1"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A27" s="1"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A28" s="1"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A29" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A13:A18"/>
+    <mergeCell ref="A20:A25"/>
+    <mergeCell ref="A27:A29"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>